--- a/plantillas/eleccion/Resultado_Computo_Total_Mesa.xlsx
+++ b/plantillas/eleccion/Resultado_Computo_Total_Mesa.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Visual Studio Code\NodeJS\SIVACC\plantillas\eleccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1626FC5A-458A-4B20-9C84-2BF80F5C9CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A8A51F-3D29-45D4-917B-B6858A26E399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A4A74427-8CFC-472D-9C29-4E23C2DF1387}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A4A74427-8CFC-472D-9C29-4E23C2DF1387}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -199,7 +199,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -556,7 +556,7 @@
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
     </row>
-    <row r="3" spans="1:14" ht="18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
     </row>
@@ -569,13 +569,16 @@
       <c r="B6" s="3"/>
     </row>
     <row r="8" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="6"/>
       <c r="B8" s="6"/>
-      <c r="M8" s="1" t="s">
+      <c r="M8" s="1"/>
+      <c r="N8" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="M9" s="1" t="s">
+      <c r="M9" s="1"/>
+      <c r="N9" s="1" t="s">
         <v>14</v>
       </c>
     </row>
